--- a/dataset/01.w_Defects/st_underrun.xlsx
+++ b/dataset/01.w_Defects/st_underrun.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>typedef struct { char buf[10]; char buf1[10]; char buf2[10]; char buf3[10]; char buf4[10]; } st_underrun_003_s_001; extern volatile int vflag; void st_underrun_003 () { st_underrun_003_s_001 s; st_underrun_003_func_001(&amp;s); st_underrun_003_func_002(&amp;s); } void st_underrun_003_func_001 (st_underrun_003_s_001 *s) { char buf[10] = "STRING"; strcpy(s-&gt;buf,buf); } void st_underrun_003_func_002 (st_underrun_003_s_001 *s) { int len = strlen(s-&gt;buf) - 1; do { s-&gt;buf[len] = 'A'; len--; /* if (s-&gt;buf[len] == '\0') break; */ }while (s-&gt;buf[len] != 'Z');/*Tool should detect this line as error*/ /* Stack Under RUN error */ }</t>
+          <t>typedef struct { char buf[10]; char buf1[10]; char buf2[10]; char buf3[10]; char buf4[10]; } st_underrun_003_s_001; extern volatile int vflag; void st_underrun_003 () { st_underrun_003_s_001 s; st_underrun_003_func_001(&amp;s); st_underrun_003_func_002(&amp;s); } void st_underrun_003_func_002 (st_underrun_003_s_001 *s) { int len = strlen(s-&gt;buf) - 1; do { s-&gt;buf[len] = 'A'; len--; /* if (s-&gt;buf[len] == '\0') break; */ }while (s-&gt;buf[len] != 'Z');/*Tool should detect this line as error*/ /* Stack Under RUN error */ } void st_underrun_003_func_001 (st_underrun_003_s_001 *s) { char buf[10] = "STRING"; strcpy(s-&gt;buf,buf); }</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
